--- a/src/test/resources/payload.xlsx
+++ b/src/test/resources/payload.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\signity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DA87AEE-C678-4209-B9B1-C6B3833DCEA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F693716-3A1F-4AE8-9680-F2D0790A79D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="27">
   <si>
     <t>merchantId</t>
   </si>
@@ -48,46 +48,64 @@
     <t>merchant_simar</t>
   </si>
   <si>
-    <t>https://crawldemolinksnew.signitydemo.in</t>
-  </si>
-  <si>
     <t>isDfs</t>
   </si>
   <si>
-    <t>https://apnews.com</t>
-  </si>
-  <si>
-    <t>https://moneyeh.ca</t>
-  </si>
-  <si>
-    <t>https://www.buzzfeed.com/ca</t>
-  </si>
-  <si>
-    <t>https://www.python.org</t>
-  </si>
-  <si>
-    <t>https://news.ycombinator.com/news</t>
-  </si>
-  <si>
-    <t>https://stackoverflow.com</t>
-  </si>
-  <si>
-    <t>https://www.geeksforgeeks.org</t>
-  </si>
-  <si>
-    <t>https://crawler-test.com/</t>
-  </si>
-  <si>
-    <t>https://merdeka.com</t>
-  </si>
-  <si>
-    <t>https://milesopedia.com</t>
-  </si>
-  <si>
-    <t>https://milesopedia.typeform.com</t>
-  </si>
-  <si>
-    <t>https://modrinth.com</t>
+    <t>https://m.youtube.com</t>
+  </si>
+  <si>
+    <t>https://nerdwallet.com</t>
+  </si>
+  <si>
+    <t>https://newsweek.com</t>
+  </si>
+  <si>
+    <t>https://rebatesme.com</t>
+  </si>
+  <si>
+    <t>https://redflagdeals.com</t>
+  </si>
+  <si>
+    <t>https://smartmoneyhabits.com</t>
+  </si>
+  <si>
+    <t>https://thechexyrundown.beehiiv.com</t>
+  </si>
+  <si>
+    <t>https://theinformr.com</t>
+  </si>
+  <si>
+    <t>https://thestar.com</t>
+  </si>
+  <si>
+    <t>https://theverge.com</t>
+  </si>
+  <si>
+    <t>https://time.com</t>
+  </si>
+  <si>
+    <t>https://planhub.ca</t>
+  </si>
+  <si>
+    <t>https://retirehappy.ca</t>
+  </si>
+  <si>
+    <t>https://simplerate.ca</t>
+  </si>
+  <si>
+    <t>https://smartwealthfinancial.ca</t>
+  </si>
+  <si>
+    <t>https://stockscanada.ca</t>
+  </si>
+  <si>
+    <t>https://tangerine.ca</t>
+  </si>
+  <si>
+    <t>https://offerhub.ca</t>
+  </si>
+  <si>
+    <t>https://myownadvisor.ca</t>
   </si>
 </sst>
 </file>
@@ -416,11 +434,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.77734375" customWidth="1"/>
-    <col min="2" max="2" width="46.5546875" customWidth="1"/>
+    <col min="2" max="2" width="112.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
     <col min="5" max="5" width="14.88671875" customWidth="1"/>
     <col min="6" max="6" width="13.88671875" customWidth="1"/>
@@ -447,7 +465,7 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -455,13 +473,13 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -478,7 +496,7 @@
         <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -501,10 +519,10 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
@@ -524,10 +542,10 @@
         <v>6</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
@@ -547,16 +565,16 @@
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
       </c>
       <c r="E6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -570,16 +588,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -593,16 +611,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
       </c>
       <c r="E8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -616,16 +634,16 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
       </c>
       <c r="E9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -639,7 +657,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -651,7 +669,7 @@
         <v>1</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
@@ -662,7 +680,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -674,7 +692,7 @@
         <v>1</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
@@ -685,7 +703,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -697,7 +715,7 @@
         <v>1</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
@@ -708,7 +726,7 @@
         <v>6</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -720,7 +738,7 @@
         <v>1</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="b">
         <v>1</v>
@@ -731,7 +749,7 @@
         <v>6</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -743,7 +761,7 @@
         <v>1</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
@@ -754,7 +772,7 @@
         <v>6</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -766,7 +784,7 @@
         <v>1</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="b">
         <v>1</v>
@@ -777,7 +795,7 @@
         <v>6</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -789,7 +807,7 @@
         <v>1</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" t="b">
         <v>1</v>
@@ -800,7 +818,7 @@
         <v>6</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -812,7 +830,7 @@
         <v>1</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="b">
         <v>1</v>
@@ -823,7 +841,7 @@
         <v>6</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -835,7 +853,7 @@
         <v>1</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
@@ -846,7 +864,7 @@
         <v>6</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -858,7 +876,7 @@
         <v>1</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
@@ -869,7 +887,7 @@
         <v>6</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -881,58 +899,33 @@
         <v>1</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>6</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21" t="b">
-        <v>1</v>
-      </c>
-      <c r="E21" t="b">
-        <v>1</v>
-      </c>
-      <c r="F21">
-        <v>1</v>
-      </c>
-      <c r="G21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B22" s="1"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B23" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{12F6FFE4-13A6-445B-8E67-893BE91820D9}"/>
-    <hyperlink ref="B3:B5" r:id="rId2" display="https://crawldemolinksnew.signitydemo.in" xr:uid="{F1161051-3346-4C56-A5BD-27BDDB741586}"/>
-    <hyperlink ref="B6:B9" r:id="rId3" display="https://crawldemolinksnew.signitydemo.in" xr:uid="{8B31FD30-2E19-478B-928B-86549A5E4148}"/>
-    <hyperlink ref="B10" r:id="rId4" xr:uid="{7D5DBAEA-9F5D-4D09-ADA6-63C375A19A93}"/>
-    <hyperlink ref="B11" r:id="rId5" xr:uid="{9BB5C471-96EE-4F58-AA41-328D8C3615DC}"/>
-    <hyperlink ref="B12" r:id="rId6" xr:uid="{5FBA42C4-4916-47B8-BD73-4945D2B20A75}"/>
-    <hyperlink ref="B13" r:id="rId7" xr:uid="{1F3496B1-3556-4D0F-BAD3-9050D0E92C52}"/>
-    <hyperlink ref="B14" r:id="rId8" xr:uid="{DA8B4FDF-6AE2-414C-83A7-59F86B853864}"/>
-    <hyperlink ref="B16" r:id="rId9" xr:uid="{CBD056CA-B649-46BE-8D62-1364A43C241F}"/>
-    <hyperlink ref="B17" r:id="rId10" xr:uid="{355333CC-03FB-43C1-92E8-74551FF44877}"/>
-    <hyperlink ref="B18" r:id="rId11" display="https://merdeka.co/" xr:uid="{9EB3A2EC-FAA4-405F-98E0-9D8093766F38}"/>
-    <hyperlink ref="B19" r:id="rId12" display="https://milesopedia.co/" xr:uid="{85A3DA68-2379-4767-95FF-7E08CAF76AF6}"/>
-    <hyperlink ref="B20" r:id="rId13" display="https://milesopedia.typeform.co/" xr:uid="{39491632-F05B-4B03-BE00-AA2884D9CDCA}"/>
-    <hyperlink ref="B21" r:id="rId14" display="https://modrinth.co/" xr:uid="{115FAB4B-7DCC-46FB-B8FE-950524005AB2}"/>
-    <hyperlink ref="B15" r:id="rId15" xr:uid="{E596645F-91B3-4026-A7AC-CCA868614F28}"/>
+    <hyperlink ref="B2" r:id="rId1" display="https://m.youtube.co/" xr:uid="{75423A90-37A6-45C0-8E1E-9BE73A4CB0A7}"/>
+    <hyperlink ref="B4" r:id="rId2" display="https://nerdwallet.co/" xr:uid="{30A4A07A-6A3F-4DA6-92BE-0964BD439CBE}"/>
+    <hyperlink ref="B5" r:id="rId3" display="https://newsweek.co/" xr:uid="{A25C8AA0-3EA0-4759-9604-7C4CC41A900A}"/>
+    <hyperlink ref="B8" r:id="rId4" display="https://rebatesme.co/" xr:uid="{A6F4682C-E4AF-4299-B3DA-7359E755E75E}"/>
+    <hyperlink ref="B9" r:id="rId5" display="https://redflagdeals.co/" xr:uid="{2F4BD261-380F-4A94-9689-03C5EF193FB7}"/>
+    <hyperlink ref="B12" r:id="rId6" display="https://smartmoneyhabits.co/" xr:uid="{11F8FA64-F21E-4782-84D1-E7CF6879F696}"/>
+    <hyperlink ref="B16" r:id="rId7" display="https://thechexyrundown.beehiiv.co/" xr:uid="{AF5AB8D9-CCEC-44FE-A163-519C0EE64C77}"/>
+    <hyperlink ref="B17" r:id="rId8" display="https://theinformr.co/" xr:uid="{48572DFE-819E-4165-B025-A0E323631CB7}"/>
+    <hyperlink ref="B18" r:id="rId9" display="https://thestar.co/" xr:uid="{B9904C78-066E-42BB-8AFD-9221BBEAC719}"/>
+    <hyperlink ref="B19" r:id="rId10" display="https://theverge.co/" xr:uid="{C8388D7D-4864-4D52-9A96-98E25B9CB84B}"/>
+    <hyperlink ref="B20" r:id="rId11" display="https://time.co/" xr:uid="{191124EF-D94B-4263-9C0B-3D0336A76944}"/>
+    <hyperlink ref="B3" r:id="rId12" xr:uid="{AB7542EF-C85E-4042-AE06-CFFC1A867403}"/>
+    <hyperlink ref="B7" r:id="rId13" xr:uid="{E01EE4D6-FBF9-4622-90AB-89A69DCA97B1}"/>
+    <hyperlink ref="B11" r:id="rId14" xr:uid="{E099850D-EA40-4C62-A13E-13771726A301}"/>
+    <hyperlink ref="B10" r:id="rId15" xr:uid="{BB717837-C356-4162-A47E-B0329156CDC4}"/>
+    <hyperlink ref="B13" r:id="rId16" xr:uid="{B507DD3E-AA67-4A7E-9CFA-AC307CEB6558}"/>
+    <hyperlink ref="B14" r:id="rId17" xr:uid="{871C9AEF-73F5-466A-905D-5C5BE088AC4D}"/>
+    <hyperlink ref="B15" r:id="rId18" xr:uid="{AFE0D0B2-D4CA-4F57-8571-9C5371A9A9AD}"/>
+    <hyperlink ref="B6" r:id="rId19" xr:uid="{1E822DD5-E0DF-4EA4-B4F9-BE7D12E95819}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
